--- a/excel/PROMOCIONES.xlsx
+++ b/excel/PROMOCIONES.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>CODIGO_PRODUCTO</t>
   </si>
@@ -41,13 +41,19 @@
     <t>GRUPOS</t>
   </si>
   <si>
-    <t>GRUPO_SINPAR</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
-    <t>SPDARC115160222</t>
+    <t>CANTIDAD_MINIMA</t>
+  </si>
+  <si>
+    <t>DOSF1601</t>
+  </si>
+  <si>
+    <t>PREMIUM TOP</t>
+  </si>
+  <si>
+    <t>PREMIUM</t>
   </si>
 </sst>
 </file>
@@ -83,9 +89,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -366,13 +373,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -388,22 +397,48 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>432.24099999999999</v>
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2719.5</v>
       </c>
       <c r="D2" s="1">
-        <v>45657</v>
+        <v>46289</v>
       </c>
       <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2719.5</v>
+      </c>
+      <c r="D3" s="1">
+        <v>46289</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/excel/PROMOCIONES.xlsx
+++ b/excel/PROMOCIONES.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>CODIGO_PRODUCTO</t>
   </si>
@@ -50,10 +50,7 @@
     <t>DOSF1601</t>
   </si>
   <si>
-    <t>PREMIUM TOP</t>
-  </si>
-  <si>
-    <t>PREMIUM</t>
+    <t>PREMIUM.PREMIUM TOP</t>
   </si>
 </sst>
 </file>
@@ -373,11 +370,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
-    <col min="5" max="5" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -421,26 +418,6 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2719.5</v>
-      </c>
-      <c r="D3" s="1">
-        <v>46289</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel/PROMOCIONES.xlsx
+++ b/excel/PROMOCIONES.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>CODIGO_PRODUCTO</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>PREMIUM.PREMIUM TOP</t>
+  </si>
+  <si>
+    <t>SF06491</t>
   </si>
 </sst>
 </file>
@@ -370,7 +373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
@@ -418,6 +421,26 @@
         <v>75</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>5475.05</v>
+      </c>
+      <c r="D3" s="1">
+        <v>46289</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel/PROMOCIONES.xlsx
+++ b/excel/PROMOCIONES.xlsx
@@ -412,7 +412,7 @@
         <v>2719.5</v>
       </c>
       <c r="D2" s="1">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -432,7 +432,7 @@
         <v>5475.05</v>
       </c>
       <c r="D3" s="1">
-        <v>46289</v>
+        <v>46292</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>

--- a/excel/PROMOCIONES.xlsx
+++ b/excel/PROMOCIONES.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ferremax-catalogo\excel\"/>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="29">
   <si>
     <t>CODIGO_PRODUCTO</t>
   </si>
@@ -47,26 +47,89 @@
     <t>CANTIDAD_MINIMA</t>
   </si>
   <si>
-    <t>DOSF1601</t>
-  </si>
-  <si>
-    <t>PREMIUM.PREMIUM TOP</t>
+    <t>SPDARC115160222</t>
+  </si>
+  <si>
+    <t>RECURRENTE_&gt;_500K.PREMIUM.PREMIUM TOP</t>
+  </si>
+  <si>
+    <t>SF08000</t>
+  </si>
+  <si>
+    <t>SF08003</t>
+  </si>
+  <si>
+    <t>SF08001</t>
+  </si>
+  <si>
+    <t>SF08004</t>
+  </si>
+  <si>
+    <t>SF06492</t>
   </si>
   <si>
     <t>SF06491</t>
+  </si>
+  <si>
+    <t>SF06496</t>
+  </si>
+  <si>
+    <t>SF06494</t>
+  </si>
+  <si>
+    <t>SF07202</t>
+  </si>
+  <si>
+    <t>SF07200</t>
+  </si>
+  <si>
+    <t>SF07199</t>
+  </si>
+  <si>
+    <t>SF07206</t>
+  </si>
+  <si>
+    <t>ROT98128</t>
+  </si>
+  <si>
+    <t>ROT98127</t>
+  </si>
+  <si>
+    <t>SF16012</t>
+  </si>
+  <si>
+    <t>SF16001</t>
+  </si>
+  <si>
+    <t>EA5305AZ</t>
+  </si>
+  <si>
+    <t>EA5310AZ</t>
+  </si>
+  <si>
+    <t>AR855300</t>
+  </si>
+  <si>
+    <t>AR855500</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -77,10 +140,36 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
+      <top style="thin">
+        <color indexed="22"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -89,10 +178,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -373,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
@@ -409,16 +510,16 @@
         <v>5</v>
       </c>
       <c r="C2" s="2">
-        <v>2719.5</v>
+        <v>485.2</v>
       </c>
       <c r="D2" s="1">
-        <v>46292</v>
+        <v>46318</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -428,17 +529,397 @@
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3">
-        <v>5475.05</v>
+      <c r="C3" s="3">
+        <v>7186</v>
       </c>
       <c r="D3" s="1">
-        <v>46292</v>
+        <v>46318</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3">
         <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>14372.01</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>11976.66</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>23953.31</v>
+      </c>
+      <c r="D6" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3">
+        <v>9581.33</v>
+      </c>
+      <c r="D7" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>5748.8</v>
+      </c>
+      <c r="D8" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3">
+        <v>11497.51</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>19162.66</v>
+      </c>
+      <c r="D10" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3">
+        <v>45838.86</v>
+      </c>
+      <c r="D11" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3">
+        <v>22919.47</v>
+      </c>
+      <c r="D12" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3">
+        <v>13751.64</v>
+      </c>
+      <c r="D13" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3">
+        <v>27503.31</v>
+      </c>
+      <c r="D14" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3">
+        <v>117804.09</v>
+      </c>
+      <c r="D15" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3">
+        <v>117804.09</v>
+      </c>
+      <c r="D16" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="6">
+        <v>47949.9</v>
+      </c>
+      <c r="D17" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="6">
+        <v>37086.699999999997</v>
+      </c>
+      <c r="D18" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="6">
+        <v>32692.2</v>
+      </c>
+      <c r="D19" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="6">
+        <v>32692.2</v>
+      </c>
+      <c r="D20" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="6">
+        <v>4141.5</v>
+      </c>
+      <c r="D21" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="6">
+        <v>5914.1</v>
+      </c>
+      <c r="D22" s="1">
+        <v>46318</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
